--- a/net-configurator/input/sample-2-8-9-800.xlsx
+++ b/net-configurator/input/sample-2-8-9-800.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="17730" yWindow="2895" windowWidth="29850" windowHeight="16380" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="34305" yWindow="6945" windowWidth="17310" windowHeight="6960" tabRatio="600" firstSheet="2" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nodes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Loopbacks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VLANs &amp; Profiles" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wire Map" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Air_Only" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Settings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Nodes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Loopbacks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="VLANs &amp; Profiles" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Wire Map" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Air_Only" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Reference" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,31 +35,6 @@
       <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF2E75B6"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
       <sz val="11"/>
     </font>
     <font>
@@ -84,8 +59,24 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="16"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -134,12 +125,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD6E4F0"/>
-        <bgColor rgb="FFD6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF305496"/>
       </patternFill>
     </fill>
@@ -155,8 +140,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEEF3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -194,11 +189,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -220,28 +225,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -273,14 +257,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -320,7 +304,7 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -351,7 +335,7 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -367,16 +351,16 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -388,19 +372,32 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Heading 1" xfId="1" builtinId="16"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -763,811 +760,835 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.85546875" customWidth="1" style="32" min="1" max="1"/>
-    <col width="86.28515625" customWidth="1" style="37" min="2" max="2"/>
-    <col width="67.140625" customWidth="1" style="32" min="3" max="3"/>
-    <col width="10" customWidth="1" style="32" min="4" max="4"/>
-    <col width="72.7109375" customWidth="1" style="62" min="5" max="5"/>
-    <col width="9.140625" customWidth="1" style="32" min="6" max="16384"/>
+    <col width="23.85546875" customWidth="1" style="25" min="1" max="1"/>
+    <col width="86.28515625" customWidth="1" style="30" min="2" max="2"/>
+    <col width="67.140625" customWidth="1" style="25" min="3" max="3"/>
+    <col width="10" customWidth="1" style="25" min="4" max="4"/>
+    <col width="72.7109375" customWidth="1" style="55" min="5" max="5"/>
+    <col width="9.140625" customWidth="1" style="25" min="6" max="8"/>
+    <col width="9.140625" customWidth="1" style="25" min="9" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>GENERAL</t>
         </is>
       </c>
-      <c r="B1" s="31" t="n"/>
-      <c r="C1" s="31" t="n"/>
-      <c r="D1" s="31" t="n"/>
-      <c r="E1" s="54" t="n"/>
+      <c r="B1" s="24" t="n"/>
+      <c r="C1" s="24" t="n"/>
+      <c r="D1" s="24" t="n"/>
+      <c r="E1" s="47" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="33" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B2" s="33" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C2" s="33" t="inlineStr">
+      <c r="C2" s="26" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D2" s="33" t="inlineStr">
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E2" s="55" t="inlineStr">
+      <c r="E2" s="48" t="inlineStr">
         <is>
           <t>Default Value</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>site_name</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>Site/deployment identifier - For Air Sim name will be ERA-site-architecture</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E3" s="49" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="C3" s="34" t="inlineStr">
-        <is>
-          <t>Site/deployment identifier - For Air Sim name will be ERA-site-architecture</t>
-        </is>
-      </c>
-      <c r="D3" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E3" s="56" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>architecture</t>
         </is>
       </c>
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>2-8-9-800</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>Deployment architecture type</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E4" s="56" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>2-8-9-800</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="E5" s="57" t="n"/>
+      <c r="E5" s="50" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>AIR DEPLOYMENT</t>
         </is>
       </c>
-      <c r="B6" s="39" t="n"/>
-      <c r="C6" s="38" t="n"/>
-      <c r="D6" s="38" t="n"/>
-      <c r="E6" s="58" t="n"/>
+      <c r="B6" s="32" t="n"/>
+      <c r="C6" s="31" t="n"/>
+      <c r="D6" s="31" t="n"/>
+      <c r="E6" s="51" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B7" s="41" t="n"/>
-      <c r="C7" s="40" t="n"/>
-      <c r="D7" s="40" t="n"/>
-      <c r="E7" s="59" t="n"/>
+      <c r="B7" s="34" t="n"/>
+      <c r="C7" s="33" t="n"/>
+      <c r="D7" s="33" t="n"/>
+      <c r="E7" s="52" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>deploy_in_air</t>
         </is>
       </c>
-      <c r="B8" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Deploy topology in NVIDIA Air (Yes/No) - Run make air-setup to set up environment to automate air deployment</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E8" s="56" t="inlineStr">
+      <c r="E8" s="49" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>status_page_enabled</t>
         </is>
       </c>
-      <c r="B9" s="42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Enable http status page for ztp server</t>
         </is>
       </c>
-      <c r="D9" s="43" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E9" s="56" t="inlineStr">
+      <c r="E9" s="49" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="E10" s="57" t="n"/>
+      <c r="E10" s="50" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="44" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>NETWORK</t>
         </is>
       </c>
-      <c r="B11" s="45" t="n"/>
-      <c r="C11" s="46" t="n"/>
-      <c r="D11" s="46" t="n"/>
-      <c r="E11" s="60" t="n"/>
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="39" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="53" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D12" s="33" t="inlineStr">
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E12" s="55" t="inlineStr">
+      <c r="E12" s="48" t="inlineStr">
         <is>
           <t>Default Value</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="45" customHeight="1" s="64">
-      <c r="A13" s="34" t="inlineStr">
+    <row r="13" ht="45" customHeight="1" s="59">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>mgmt_subnets</t>
         </is>
       </c>
-      <c r="B13" s="47" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>192.168.200.0/24</t>
         </is>
       </c>
-      <c r="C13" s="48" t="inlineStr">
+      <c r="C13" s="41" t="inlineStr">
         <is>
           <t>Management subnets (comma-separated list) - either use 1 for all or 1 subnet per management switch. For now, use 1 subnet if doing L3 oob.</t>
         </is>
       </c>
-      <c r="D13" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E13" s="56" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E13" s="49" t="inlineStr">
         <is>
           <t>192.168.200.0/24</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>management_switches</t>
         </is>
       </c>
-      <c r="B14" s="47" t="n">
+      <c r="B14" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="48" t="inlineStr">
+      <c r="C14" s="41" t="inlineStr">
         <is>
           <t>Number of OOB management switches</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E14" s="56" t="n">
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E14" s="49" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" s="64">
-      <c r="A15" s="34" t="inlineStr">
-        <is>
-          <t>tiers</t>
-        </is>
-      </c>
-      <c r="B15" s="42" t="n">
+    <row r="15" ht="30" customHeight="1" s="59">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>ns_tiers</t>
+        </is>
+      </c>
+      <c r="B15" s="62" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="48" t="inlineStr">
-        <is>
-          <t>Network tiers (1=collapsed, 2=spine-leaf) - 1 is the only valid option now</t>
-        </is>
-      </c>
-      <c r="D15" s="36" t="inlineStr">
+      <c r="C15" s="41" t="inlineStr">
+        <is>
+          <t>Network tiers (1=collapsed, 2=spine-leaf) on North-South Network</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E15" s="49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" s="59">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>ew_tiers</t>
+        </is>
+      </c>
+      <c r="B16" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="41" t="inlineStr">
+        <is>
+          <t>Network tiers (1=collapsed, 2=spine-leaf) on East-West GPU Network</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E16" s="49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" s="59">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>convergence</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="inlineStr">
+        <is>
+          <t>dedicated_gpu</t>
+        </is>
+      </c>
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>Convergence mode: full or dedicated_gpu - if converged ns_tiers and ew_tiers should both be 1</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E15" s="56" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" s="64">
-      <c r="A16" s="34" t="inlineStr">
-        <is>
-          <t>convergence</t>
-        </is>
-      </c>
-      <c r="B16" s="42" t="inlineStr">
+      <c r="E17" s="49" t="inlineStr">
         <is>
           <t>dedicated_gpu</t>
         </is>
       </c>
-      <c r="C16" s="48" t="inlineStr">
-        <is>
-          <t>Convergence mode: full or dedicated_gpu - full is the only valid option now if not 2-8-9-800 architecture</t>
-        </is>
-      </c>
-      <c r="D16" s="36" t="inlineStr">
+    </row>
+    <row r="18" ht="45" customHeight="1" s="59">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>gpu_planes</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="41" t="inlineStr">
+        <is>
+          <t>Number of GPU compute fabric planes (1=single, 2=dual). 2 is only valid for 2-8-9-800 right now --&gt; and currently IS the only valid option for 2-8-9-800</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E16" s="56" t="inlineStr">
-        <is>
-          <t>dedicated_gpu</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" s="64">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>gpu_planes</t>
-        </is>
-      </c>
-      <c r="B17" s="42" t="n">
+      <c r="E18" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="48" t="inlineStr">
-        <is>
-          <t>Number of GPU compute fabric planes (1=single, 2=dual). 2 is only valid for 2-8-9-800 right now --&gt; and currently IS the only valid option for 2-8-9-800</t>
-        </is>
-      </c>
-      <c r="D17" s="36" t="inlineStr">
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>bgp_asn</t>
+        </is>
+      </c>
+      <c r="B19" s="40" t="n">
+        <v>4260394788</v>
+      </c>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t>BGP Autonomous System Number</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E19" s="49" t="n">
+        <v>4260394788</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>loopback_base</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>172.16.176</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t>Loopback IP base (first 3 octets)</t>
+        </is>
+      </c>
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E17" s="56" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="34" t="inlineStr">
-        <is>
-          <t>bgp_asn</t>
-        </is>
-      </c>
-      <c r="B18" s="47" t="n">
-        <v>4260394788</v>
-      </c>
-      <c r="C18" s="48" t="inlineStr">
-        <is>
-          <t>BGP Autonomous System Number</t>
-        </is>
-      </c>
-      <c r="D18" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E18" s="56" t="n">
-        <v>4260394788</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="34" t="inlineStr">
-        <is>
-          <t>loopback_base</t>
-        </is>
-      </c>
-      <c r="B19" s="42" t="inlineStr">
+      <c r="E20" s="49" t="inlineStr">
         <is>
           <t>172.16.176</t>
         </is>
       </c>
-      <c r="C19" s="48" t="inlineStr">
-        <is>
-          <t>Loopback IP base (first 3 octets)</t>
-        </is>
-      </c>
-      <c r="D19" s="36" t="inlineStr">
+    </row>
+    <row r="21" ht="30" customHeight="1" s="59">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>disabled_ports</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C21" s="41" t="inlineStr">
+        <is>
+          <t>Disabled/unused port numbers (comma-separated)</t>
+        </is>
+      </c>
+      <c r="D21" s="29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E19" s="56" t="inlineStr">
-        <is>
-          <t>172.16.176</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="34" t="inlineStr">
-        <is>
-          <t>disabled_ports</t>
-        </is>
-      </c>
-      <c r="B20" s="42" t="inlineStr">
+      <c r="E21" s="49" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="C20" s="48" t="inlineStr">
-        <is>
-          <t>Disabled/unused port numbers (comma-separated)</t>
-        </is>
-      </c>
-      <c r="D20" s="36" t="inlineStr">
+    </row>
+    <row r="22" ht="45" customHeight="1" s="59">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>gpu_vlan_mode</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="C22" s="41" t="inlineStr">
+        <is>
+          <t>GPU VLAN topology. Valid values: 'single' (one GPU VLAN — default), 'per_rail' (one VLAN per rail; requires gpu_rail&lt;N&gt; rows in VLANs &amp; Profiles), 'per_rail_per_plane' (one VLAN per (rail, plane); requires gpu_rail&lt;R&gt;_plane&lt;P&gt; rows).</t>
+        </is>
+      </c>
+      <c r="D22" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E20" s="56" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1" s="64">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
-          <t>gpu_vlan_mode</t>
-        </is>
-      </c>
-      <c r="B21" s="42" t="inlineStr">
+      <c r="E22" s="49" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="C21" s="48" t="inlineStr">
-        <is>
-          <t>GPU VLAN topology. Valid values: 'single' (one GPU VLAN — default), 'per_rail' (one VLAN per rail; requires gpu_rail&lt;N&gt; rows in VLANs &amp; Profiles), 'per_rail_per_plane' (one VLAN per (rail, plane); requires gpu_rail&lt;R&gt;_plane&lt;P&gt; rows).</t>
-        </is>
-      </c>
-      <c r="D21" s="43" t="inlineStr">
+    </row>
+    <row r="23" ht="30" customHeight="1" s="59">
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>oob_uplink_mode</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t>OOB uplink topology. Accepted case-insensitively: l2/L2 or l3/L3. Use l2 for legacy bridged/bonded uplinks or l3 for direct routed uplinks.</t>
+        </is>
+      </c>
+      <c r="D23" s="36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E21" s="56" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1" s="64">
-      <c r="A22" s="34" t="inlineStr">
-        <is>
-          <t>oob_uplink_mode</t>
-        </is>
-      </c>
-      <c r="B22" s="42" t="inlineStr">
+      <c r="E23" s="49" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="C22" s="48" t="inlineStr">
-        <is>
-          <t>OOB uplink topology. Accepted case-insensitively: l2/L2 or l3/L3. Use l2 for legacy bridged/bonded uplinks or l3 for direct routed uplinks.</t>
-        </is>
-      </c>
-      <c r="D22" s="43" t="inlineStr">
+    </row>
+    <row r="24">
+      <c r="E24" s="50" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="B25" s="38" t="n"/>
+      <c r="C25" s="39" t="n"/>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="53" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B26" s="42" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C26" s="42" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D26" s="42" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="E26" s="48" t="inlineStr">
+        <is>
+          <t>Default Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>ldap_enabled</t>
+        </is>
+      </c>
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E22" s="56" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="E23" s="57" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="46" t="inlineStr">
-        <is>
-          <t>MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="B24" s="45" t="n"/>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="60" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="49" t="inlineStr">
+      <c r="C27" s="27" t="inlineStr">
+        <is>
+          <t>Enable LDAP authentication (Yes/No)</t>
+        </is>
+      </c>
+      <c r="D27" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E27" s="49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>ldap_domain</t>
+        </is>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>example.com</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="inlineStr">
+        <is>
+          <t>LDAP domain name</t>
+        </is>
+      </c>
+      <c r="D28" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E28" s="49" t="inlineStr">
+        <is>
+          <t>example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1" s="59">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>ldap_base_dn</t>
+        </is>
+      </c>
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>dc=example,dc=com</t>
+        </is>
+      </c>
+      <c r="C29" s="27" t="inlineStr">
+        <is>
+          <t>LDAP base DN</t>
+        </is>
+      </c>
+      <c r="D29" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E29" s="49" t="inlineStr">
+        <is>
+          <t>dc=example,dc=com</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1" s="59">
+      <c r="A30" s="27" t="inlineStr">
+        <is>
+          <t>ldap_root_dn</t>
+        </is>
+      </c>
+      <c r="B30" s="35" t="inlineStr">
+        <is>
+          <t>cn=admin,ou=Users,dc=example,dc=com</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="inlineStr">
+        <is>
+          <t>LDAP bind DN for switch authentication</t>
+        </is>
+      </c>
+      <c r="D30" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E30" s="49" t="inlineStr">
+        <is>
+          <t>cn=admin,ou=Users,dc=example,dc=com</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1" s="59">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>ldap_servers</t>
+        </is>
+      </c>
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>172.20.0.78</t>
+        </is>
+      </c>
+      <c r="C31" s="41" t="inlineStr">
+        <is>
+          <t>LDAP server IPs (comma-separated, in priority order). Note, in Air use 172.20.0.78 for L3 oob and 172.20.0.77 for L2 OOB</t>
+        </is>
+      </c>
+      <c r="D31" s="29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E31" s="49" t="inlineStr">
+        <is>
+          <t>172.20.0.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="E32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="39" t="inlineStr">
+        <is>
+          <t>TELEMETRY</t>
+        </is>
+      </c>
+      <c r="B33" s="38" t="n"/>
+      <c r="C33" s="39" t="n"/>
+      <c r="D33" s="39" t="n"/>
+      <c r="E33" s="53" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="42" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B25" s="49" t="inlineStr">
+      <c r="B34" s="42" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C25" s="49" t="inlineStr">
+      <c r="C34" s="42" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D25" s="49" t="inlineStr">
+      <c r="D34" s="42" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E25" s="55" t="inlineStr">
+      <c r="E34" s="48" t="inlineStr">
         <is>
           <t>Default Value</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="34" t="inlineStr">
-        <is>
-          <t>ldap_enabled</t>
-        </is>
-      </c>
-      <c r="B26" s="42" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>netq_ip</t>
+        </is>
+      </c>
+      <c r="B35" s="35" t="n"/>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>NetQ server IP address (leave blank to skip NetQ config)</t>
+        </is>
+      </c>
+      <c r="D35" s="29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C26" s="34" t="inlineStr">
-        <is>
-          <t>Enable LDAP authentication (Yes/No)</t>
-        </is>
-      </c>
-      <c r="D26" s="36" t="inlineStr">
+      <c r="E35" s="49" t="n"/>
+    </row>
+    <row r="36">
+      <c r="E36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="37" t="inlineStr">
+        <is>
+          <t>ADVANCED</t>
+        </is>
+      </c>
+      <c r="B37" s="38" t="n"/>
+      <c r="C37" s="39" t="n"/>
+      <c r="D37" s="39" t="n"/>
+      <c r="E37" s="53" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="E38" s="48" t="inlineStr">
+        <is>
+          <t>Default Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1" s="59">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>timezone</t>
+        </is>
+      </c>
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t>Etc/Zulu</t>
+        </is>
+      </c>
+      <c r="C39" s="27" t="inlineStr">
+        <is>
+          <t>System timezone</t>
+        </is>
+      </c>
+      <c r="D39" s="29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E26" s="56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="34" t="inlineStr">
-        <is>
-          <t>ldap_domain</t>
-        </is>
-      </c>
-      <c r="B27" s="42" t="inlineStr">
-        <is>
-          <t>example.com</t>
-        </is>
-      </c>
-      <c r="C27" s="34" t="inlineStr">
-        <is>
-          <t>LDAP domain name</t>
-        </is>
-      </c>
-      <c r="D27" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E27" s="56" t="inlineStr">
-        <is>
-          <t>example.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="34" t="inlineStr">
-        <is>
-          <t>ldap_base_dn</t>
-        </is>
-      </c>
-      <c r="B28" s="42" t="inlineStr">
-        <is>
-          <t>dc=example,dc=com</t>
-        </is>
-      </c>
-      <c r="C28" s="34" t="inlineStr">
-        <is>
-          <t>LDAP base DN</t>
-        </is>
-      </c>
-      <c r="D28" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E28" s="56" t="inlineStr">
-        <is>
-          <t>dc=example,dc=com</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1" s="64">
-      <c r="A29" s="34" t="inlineStr">
-        <is>
-          <t>ldap_root_dn</t>
-        </is>
-      </c>
-      <c r="B29" s="42" t="inlineStr">
-        <is>
-          <t>cn=admin,ou=Users,dc=example,dc=com</t>
-        </is>
-      </c>
-      <c r="C29" s="34" t="inlineStr">
-        <is>
-          <t>LDAP bind DN for switch authentication</t>
-        </is>
-      </c>
-      <c r="D29" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E29" s="56" t="inlineStr">
-        <is>
-          <t>cn=admin,ou=Users,dc=example,dc=com</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1" s="64">
-      <c r="A30" s="34" t="inlineStr">
-        <is>
-          <t>ldap_servers</t>
-        </is>
-      </c>
-      <c r="B30" s="42" t="inlineStr">
-        <is>
-          <t>172.20.0.78</t>
-        </is>
-      </c>
-      <c r="C30" s="48" t="inlineStr">
-        <is>
-          <t>LDAP server IPs (comma-separated, in priority order). Note, in Air use 172.20.0.78 for L3 oob and 172.20.0.77 for L2 OOB</t>
-        </is>
-      </c>
-      <c r="D30" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E30" s="56" t="inlineStr">
-        <is>
-          <t>172.20.0.78</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="E31" s="57" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="46" t="inlineStr">
-        <is>
-          <t>TELEMETRY</t>
-        </is>
-      </c>
-      <c r="B32" s="45" t="n"/>
-      <c r="C32" s="46" t="n"/>
-      <c r="D32" s="46" t="n"/>
-      <c r="E32" s="60" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="49" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="B33" s="49" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C33" s="49" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D33" s="49" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="E33" s="55" t="inlineStr">
-        <is>
-          <t>Default Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="34" t="inlineStr">
-        <is>
-          <t>netq_ip</t>
-        </is>
-      </c>
-      <c r="B34" s="42" t="n"/>
-      <c r="C34" s="34" t="inlineStr">
-        <is>
-          <t>NetQ server IP address (leave blank to skip NetQ config)</t>
-        </is>
-      </c>
-      <c r="D34" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E34" s="56" t="n"/>
-    </row>
-    <row r="35">
-      <c r="E35" s="57" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="44" t="inlineStr">
-        <is>
-          <t>ADVANCED</t>
-        </is>
-      </c>
-      <c r="B36" s="45" t="n"/>
-      <c r="C36" s="46" t="n"/>
-      <c r="D36" s="46" t="n"/>
-      <c r="E36" s="60" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="33" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="B37" s="33" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C37" s="33" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D37" s="33" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="E37" s="55" t="inlineStr">
-        <is>
-          <t>Default Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="34" t="inlineStr">
-        <is>
-          <t>timezone</t>
-        </is>
-      </c>
-      <c r="B38" s="50" t="inlineStr">
+      <c r="E39" s="49" t="inlineStr">
         <is>
           <t>Etc/Zulu</t>
         </is>
       </c>
-      <c r="C38" s="34" t="inlineStr">
-        <is>
-          <t>System timezone</t>
-        </is>
-      </c>
-      <c r="D38" s="36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E38" s="56" t="inlineStr">
-        <is>
-          <t>Etc/Zulu</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="45" customHeight="1" s="64">
-      <c r="A39" s="34" t="inlineStr">
+    </row>
+    <row r="40" ht="51.75" customHeight="1" s="59">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>pre_login_message</t>
         </is>
       </c>
-      <c r="B39" s="50" t="inlineStr">
+      <c r="B40" s="43" t="inlineStr">
         <is>
           <t>##############################################################################
 #      You are accessing an Information System (IS) that is provided for authorized use only.
 ##############################################################################</t>
         </is>
       </c>
-      <c r="C39" s="48" t="inlineStr">
+      <c r="C40" s="41" t="inlineStr">
         <is>
           <t>SSH pre-login banner (shown before authentication). Empty cell = no banner emitted. Supports {hostname}, {site}, {arch} placeholders.</t>
         </is>
       </c>
-      <c r="D39" s="36" t="inlineStr">
+      <c r="D40" s="29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E39" s="56" t="inlineStr">
+      <c r="E40" s="49" t="inlineStr">
         <is>
           <t>##############################################################################
 #      You are accessing an Information System (IS) that is provided for authorized use only.
@@ -1575,30 +1596,30 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="51.75" customHeight="1" s="64">
-      <c r="A40" s="34" t="inlineStr">
+    <row r="41" ht="45" customHeight="1" s="59">
+      <c r="A41" s="27" t="inlineStr">
         <is>
           <t>post_login_message</t>
         </is>
       </c>
-      <c r="B40" s="50" t="inlineStr">
+      <c r="B41" s="43" t="inlineStr">
         <is>
           <t>####################################################################
 #       You are successfully logged in to: {hostname} - site: {site} / arch: {arch}
 ####################################################################</t>
         </is>
       </c>
-      <c r="C40" s="48" t="inlineStr">
+      <c r="C41" s="41" t="inlineStr">
         <is>
           <t>Login MOTD (shown after successful authentication). Empty cell = no banner emitted. Supports {hostname}, {site}, {arch} placeholders.</t>
         </is>
       </c>
-      <c r="D40" s="36" t="inlineStr">
+      <c r="D41" s="29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E40" s="56" t="inlineStr">
+      <c r="E41" s="49" t="inlineStr">
         <is>
           <t>####################################################################
 #       You are successfully logged in to: {hostname} - site: {site} / arch: {arch}
@@ -1606,121 +1627,121 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="34" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>mh_mac</t>
         </is>
       </c>
-      <c r="B41" s="50" t="inlineStr">
+      <c r="B42" s="43" t="inlineStr">
         <is>
           <t>44:38:39:FF:00:AA</t>
         </is>
       </c>
-      <c r="C41" s="34" t="inlineStr">
+      <c r="C42" s="27" t="inlineStr">
         <is>
           <t>EVPN Multihoming system MAC</t>
         </is>
       </c>
-      <c r="D41" s="36" t="inlineStr">
+      <c r="D42" s="29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E41" s="56" t="inlineStr">
+      <c r="E42" s="49" t="inlineStr">
         <is>
           <t>44:38:39:FF:00:AA</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="34" t="inlineStr">
+    <row r="43" ht="60" customHeight="1" s="59">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>anycast_mac</t>
         </is>
       </c>
-      <c r="B42" s="50" t="inlineStr">
+      <c r="B43" s="43" t="inlineStr">
         <is>
           <t>44:38:39:ff:00:ff</t>
         </is>
       </c>
-      <c r="C42" s="34" t="inlineStr">
+      <c r="C43" s="27" t="inlineStr">
         <is>
           <t>Anycast gateway MAC</t>
         </is>
       </c>
-      <c r="D42" s="36" t="inlineStr">
+      <c r="D43" s="29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E42" s="56" t="inlineStr">
+      <c r="E43" s="49" t="inlineStr">
         <is>
           <t>44:38:39:ff:00:ff</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1" s="64">
-      <c r="A43" s="34" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t>ztp_enabled</t>
         </is>
       </c>
-      <c r="B43" s="50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C43" s="34" t="inlineStr">
+      <c r="B44" s="43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>Enable Zero Touch Provisioning (Yes/No)</t>
         </is>
       </c>
-      <c r="D43" s="36" t="inlineStr">
+      <c r="D44" s="29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E43" s="56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="34" t="inlineStr">
+      <c r="E44" s="49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1" s="59">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>ztp_server</t>
         </is>
       </c>
-      <c r="B44" s="50" t="inlineStr">
+      <c r="B45" s="43" t="inlineStr">
         <is>
           <t>192.168.200.100</t>
         </is>
       </c>
-      <c r="C44" s="34" t="inlineStr">
+      <c r="C45" s="27" t="inlineStr">
         <is>
           <t>ZTP/DHCP server IP address</t>
         </is>
       </c>
-      <c r="D44" s="36" t="inlineStr">
+      <c r="D45" s="29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E44" s="56" t="inlineStr">
+      <c r="E45" s="49" t="inlineStr">
         <is>
           <t>192.168.200.100</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1" s="64">
-      <c r="A45" s="34" t="inlineStr">
+    <row r="46" ht="60" customHeight="1" s="59">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>ntp_servers</t>
         </is>
       </c>
-      <c r="B45" s="50" t="inlineStr">
+      <c r="B46" s="43" t="inlineStr">
         <is>
           <t>0.cumulusnetworks.pool.ntp.org
 1.cumulusnetworks.pool.ntp.org
@@ -1728,17 +1749,17 @@
 3.cumulusnetworks.pool.ntp.org</t>
         </is>
       </c>
-      <c r="C45" s="34" t="inlineStr">
+      <c r="C46" s="27" t="inlineStr">
         <is>
           <t>NTP server hostnames (comma or newline separated)</t>
         </is>
       </c>
-      <c r="D45" s="36" t="inlineStr">
+      <c r="D46" s="29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E45" s="56" t="inlineStr">
+      <c r="E46" s="49" t="inlineStr">
         <is>
           <t>0.cumulusnetworks.pool.ntp.org
 1.cumulusnetworks.pool.ntp.org
@@ -1747,183 +1768,182 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="34" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="27" t="inlineStr">
         <is>
           <t>num_physical_ports</t>
         </is>
       </c>
-      <c r="B46" s="50" t="n">
+      <c r="B47" s="43" t="n">
         <v>64</v>
       </c>
-      <c r="C46" s="34" t="inlineStr">
+      <c r="C47" s="27" t="inlineStr">
         <is>
           <t>Physical ports on the core switch (SN5610 = 64)</t>
         </is>
       </c>
-      <c r="D46" s="36" t="inlineStr">
+      <c r="D47" s="29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E46" s="56" t="n">
+      <c r="E47" s="49" t="n">
         <v>64</v>
       </c>
     </row>
-    <row r="47">
-      <c r="E47" s="57" t="n"/>
-    </row>
     <row r="48">
-      <c r="A48" s="51" t="inlineStr">
+      <c r="E48" s="50" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="44" t="inlineStr">
         <is>
           <t>VERSIONS</t>
         </is>
       </c>
-      <c r="B48" s="39" t="n"/>
-      <c r="C48" s="38" t="n"/>
-      <c r="D48" s="38" t="n"/>
-      <c r="E48" s="58" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="52" t="inlineStr">
+      <c r="B49" s="32" t="n"/>
+      <c r="C49" s="31" t="n"/>
+      <c r="D49" s="31" t="n"/>
+      <c r="E49" s="51" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="45" t="inlineStr">
         <is>
           <t>Switch Function</t>
         </is>
       </c>
-      <c r="B49" s="52" t="inlineStr">
+      <c r="B50" s="45" t="inlineStr">
         <is>
           <t>Cumulus Version</t>
         </is>
       </c>
-      <c r="C49" s="52" t="inlineStr">
+      <c r="C50" s="45" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D49" s="52" t="inlineStr">
+      <c r="D50" s="45" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E49" s="55" t="inlineStr">
+      <c r="E50" s="48" t="inlineStr">
         <is>
           <t>Default Value</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="34" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="27" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="B50" s="53" t="inlineStr">
+      <c r="B51" s="46" t="inlineStr">
         <is>
           <t>5.16.1</t>
         </is>
       </c>
-      <c r="C50" s="34" t="inlineStr">
+      <c r="C51" s="27" t="inlineStr">
         <is>
           <t>Cumulus Linux version (5.16+ supported in this release)</t>
         </is>
       </c>
-      <c r="D50" s="43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E50" s="61" t="inlineStr">
+      <c r="D51" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E51" s="54" t="inlineStr">
         <is>
           <t>5.16.1</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="34" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="27" t="inlineStr">
         <is>
           <t>oob</t>
         </is>
       </c>
-      <c r="B51" s="53" t="inlineStr">
+      <c r="B52" s="46" t="inlineStr">
         <is>
           <t>5.15.1</t>
         </is>
       </c>
-      <c r="C51" s="34" t="inlineStr">
+      <c r="C52" s="27" t="inlineStr">
         <is>
           <t>Cumulus Linux version (5.15+ supported in this release)</t>
         </is>
       </c>
-      <c r="D51" s="43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E51" s="61" t="inlineStr">
+      <c r="D52" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E52" s="54" t="inlineStr">
         <is>
           <t>5.15.1</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="34" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="27" t="inlineStr">
         <is>
           <t>csl</t>
         </is>
       </c>
-      <c r="B52" s="53" t="inlineStr">
+      <c r="B53" s="46" t="inlineStr">
         <is>
           <t>5.16.1</t>
         </is>
       </c>
-      <c r="C52" s="34" t="inlineStr">
+      <c r="C53" s="27" t="inlineStr">
         <is>
           <t>Cumulus Linux version (5.16+ supported in this release)</t>
         </is>
       </c>
-      <c r="D52" s="43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E52" s="61" t="inlineStr">
+      <c r="D53" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E53" s="54" t="inlineStr">
         <is>
           <t>5.16.1</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="34" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="27" t="inlineStr">
         <is>
           <t>gsl</t>
         </is>
       </c>
-      <c r="B53" s="53" t="inlineStr">
+      <c r="B54" s="46" t="inlineStr">
         <is>
           <t>5.16.1</t>
         </is>
       </c>
-      <c r="C53" s="34" t="inlineStr">
+      <c r="C54" s="27" t="inlineStr">
         <is>
           <t>Cumulus Linux version (5.16+ supported in this release)</t>
         </is>
       </c>
-      <c r="D53" s="43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E53" s="61" t="inlineStr">
+      <c r="D54" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E54" s="54" t="inlineStr">
         <is>
           <t>5.16.1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <dataValidations count="1">
-    <dataValidation sqref="B4 E4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"2-4-3-200,2-8-5-200,2-8-9-400,2-8-9-800"</formula1>
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"2-4-3-200,2-8-5-200,2-8-9-400,2-8-9-800,2-8-9-400-SP,2-4-5-800"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1939,14 +1959,14 @@
   <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="64" min="1" max="3"/>
-    <col width="22" customWidth="1" style="64" min="4" max="4"/>
-    <col width="18" customWidth="1" style="64" min="5" max="5"/>
-    <col width="8" customWidth="1" style="64" min="6" max="6"/>
-    <col width="16" customWidth="1" style="64" min="7" max="7"/>
-    <col width="8" customWidth="1" style="30" min="8" max="8"/>
-    <col width="10" customWidth="1" style="30" min="9" max="9"/>
-    <col width="76.85546875" customWidth="1" style="27" min="10" max="10"/>
+    <col width="18" customWidth="1" style="59" min="1" max="3"/>
+    <col width="22" customWidth="1" style="59" min="4" max="4"/>
+    <col width="18" customWidth="1" style="59" min="5" max="5"/>
+    <col width="8" customWidth="1" style="59" min="6" max="6"/>
+    <col width="16" customWidth="1" style="59" min="7" max="7"/>
+    <col width="8" customWidth="1" style="23" min="8" max="8"/>
+    <col width="10" customWidth="1" style="23" min="9" max="9"/>
+    <col width="76.85546875" customWidth="1" style="20" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1995,403 +2015,403 @@
           <t>Enabled</t>
         </is>
       </c>
-      <c r="J1" s="23" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>edge</t>
         </is>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>cust-net-edge-01</t>
         </is>
       </c>
-      <c r="C2" s="28" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>switch</t>
         </is>
       </c>
-      <c r="D2" s="28" t="n"/>
-      <c r="E2" s="28" t="n"/>
-      <c r="F2" s="28" t="n"/>
-      <c r="G2" s="28" t="n"/>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="D2" s="21" t="n"/>
+      <c r="E2" s="21" t="n"/>
+      <c r="F2" s="21" t="n"/>
+      <c r="G2" s="21" t="n"/>
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I2" s="29" t="inlineStr">
+      <c r="I2" s="22" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="J2" s="28" t="inlineStr">
+      <c r="J2" s="21" t="inlineStr">
         <is>
           <t>Air-only. Customer-edge sim — air-mgmt L2 bridge + EXIT-VRF eBGP underlay</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>edge</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>cust-net-edge-02</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>switch</t>
         </is>
       </c>
-      <c r="D3" s="28" t="n"/>
-      <c r="E3" s="28" t="n"/>
-      <c r="F3" s="28" t="n"/>
-      <c r="G3" s="28" t="n"/>
-      <c r="H3" s="29" t="inlineStr">
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="21" t="n"/>
+      <c r="F3" s="21" t="n"/>
+      <c r="G3" s="21" t="n"/>
+      <c r="H3" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I3" s="29" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="J3" s="28" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t>Air-only. HA pair for NAT return path</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>external-conn</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>external-conn</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D4" s="28" t="n"/>
-      <c r="E4" s="28" t="n"/>
-      <c r="F4" s="28" t="n"/>
-      <c r="G4" s="28" t="n"/>
-      <c r="H4" s="29" t="inlineStr">
+      <c r="D4" s="21" t="n"/>
+      <c r="E4" s="21" t="n"/>
+      <c r="F4" s="21" t="n"/>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I4" s="29" t="inlineStr">
+      <c r="I4" s="22" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="J4" s="28" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t>Air-only. NAT host (172.20.0.1) — routes outbound through Air</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>external-dhcp</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>external-dhcp</t>
         </is>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="28" t="n"/>
-      <c r="F5" s="28" t="n"/>
-      <c r="G5" s="28" t="n"/>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="D5" s="21" t="n"/>
+      <c r="E5" s="21" t="n"/>
+      <c r="F5" s="21" t="n"/>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I5" s="29" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="J5" s="28" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>Air-only. ZTP DHCP server + inter-VRF EXIT relay target</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>utility</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>utility</t>
         </is>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D6" s="28" t="n"/>
-      <c r="E6" s="28" t="n"/>
-      <c r="F6" s="28" t="n"/>
-      <c r="G6" s="28" t="n"/>
-      <c r="H6" s="29" t="inlineStr">
+      <c r="D6" s="21" t="n"/>
+      <c r="E6" s="21" t="n"/>
+      <c r="F6" s="21" t="n"/>
+      <c r="G6" s="21" t="n"/>
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I6" s="29" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="J6" s="28" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>Air-only. Jumpbox + status page + OOB-side DHCP relay target</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>dhcp</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>dhcp-oob</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D7" s="28" t="n"/>
-      <c r="E7" s="28" t="n"/>
-      <c r="F7" s="28" t="n"/>
-      <c r="G7" s="28" t="n"/>
-      <c r="H7" s="29" t="inlineStr">
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I7" s="29" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="J7" s="28" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t>Air-only (L2 OOB uplink mode legacy). ZTP DHCP server on OOB</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>oob-server</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>oob-server-01</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D8" s="28" t="n"/>
-      <c r="E8" s="28" t="n"/>
-      <c r="F8" s="28" t="n"/>
-      <c r="G8" s="28" t="n"/>
-      <c r="H8" s="29" t="inlineStr">
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I8" s="29" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>Air-only (L2 OOB uplink mode legacy). OOB jumpbox</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>dhcp</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>dhcp-edge</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D9" s="28" t="n"/>
-      <c r="E9" s="28" t="n"/>
-      <c r="F9" s="28" t="n"/>
-      <c r="G9" s="28" t="n"/>
-      <c r="H9" s="29" t="inlineStr">
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="21" t="n"/>
+      <c r="F9" s="21" t="n"/>
+      <c r="G9" s="21" t="n"/>
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I9" s="29" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="J9" s="28" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t>Air-only (L2 OOB uplink mode legacy). Edge-side DHCP</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>air-oob</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>air-oob-switch</t>
         </is>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>switch</t>
         </is>
       </c>
-      <c r="D10" s="28" t="n"/>
-      <c r="E10" s="28" t="n"/>
-      <c r="F10" s="28" t="n"/>
-      <c r="G10" s="28" t="n"/>
-      <c r="H10" s="29" t="inlineStr">
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I10" s="29" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="J10" s="28" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t>Air-only (L2 OOB uplink mode legacy). OOB L2 bridge</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>ext-storage</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>ext-storage-01</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D11" s="28" t="n"/>
-      <c r="E11" s="28" t="n"/>
-      <c r="F11" s="28" t="n"/>
-      <c r="G11" s="28" t="n"/>
-      <c r="H11" s="29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I11" s="29" t="inlineStr">
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="J11" s="28" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t>External customer storage aggregate (Air-only) — simulates upstream STORAGE VRF</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>ext-storage</t>
         </is>
       </c>
-      <c r="B12" s="28" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>ext-storage-02</t>
         </is>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D12" s="28" t="n"/>
-      <c r="E12" s="28" t="n"/>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="28" t="n"/>
-      <c r="H12" s="29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I12" s="29" t="inlineStr">
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Air</t>
         </is>
       </c>
-      <c r="J12" s="28" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t>External customer storage aggregate (Air-only) — simulates upstream STORAGE VRF</t>
         </is>
@@ -2417,17 +2437,17 @@
       <c r="E13" s="8" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J13" s="24" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>CPU/Storage Leaf — converged fabric for CPU/in-band, support, storage, OOB</t>
         </is>
@@ -2463,7 +2483,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n"/>
+      <c r="J14" s="18" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -2485,17 +2505,17 @@
       <c r="E15" s="8" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>GPU plane 1 leaf — half of the dual-plane GPU fabric (L3-isolated from plane2)</t>
         </is>
@@ -2531,7 +2551,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n"/>
+      <c r="J16" s="18" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -2553,17 +2573,17 @@
       <c r="E17" s="8" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I17" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J17" s="24" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J17" s="17" t="inlineStr">
         <is>
           <t>GPU plane 2 leaf — paired with plane1 for blast-radius isolation</t>
         </is>
@@ -2599,7 +2619,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n"/>
+      <c r="J18" s="18" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -2621,17 +2641,17 @@
       <c r="E19" s="8" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I19" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J19" s="18" t="inlineStr">
         <is>
           <t>Out-of-band management switch — terminates eth0 on OOB network</t>
         </is>
@@ -2667,7 +2687,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J20" s="25" t="n"/>
+      <c r="J20" s="18" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -2677,7 +2697,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -2699,17 +2719,17 @@
           <t>192.168.200.1</t>
         </is>
       </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J21" s="24" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J21" s="17" t="inlineStr">
         <is>
           <t>GPU compute node — runs AI workloads, east-west on GPU fabric</t>
         </is>
@@ -2723,7 +2743,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -2755,7 +2775,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J22" s="25" t="n"/>
+      <c r="J22" s="18" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -2765,7 +2785,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -2787,17 +2807,17 @@
           <t>192.168.200.1</t>
         </is>
       </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I23" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J23" s="24" t="n"/>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J23" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2807,7 +2827,7 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -2839,7 +2859,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J24" s="25" t="n"/>
+      <c r="J24" s="18" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -2849,7 +2869,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -2871,17 +2891,17 @@
           <t>192.168.200.1</t>
         </is>
       </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I25" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J25" s="24" t="n"/>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J25" s="17" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2891,7 +2911,7 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -2923,7 +2943,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J26" s="25" t="n"/>
+      <c r="J26" s="18" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -2933,7 +2953,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -2955,17 +2975,17 @@
           <t>192.168.200.1</t>
         </is>
       </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I27" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J27" s="24" t="n"/>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J27" s="17" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2975,7 +2995,7 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -3007,7 +3027,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J28" s="25" t="n"/>
+      <c r="J28" s="18" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -3017,7 +3037,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>bcm-01</t>
+          <t>support-01</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -3039,17 +3059,17 @@
           <t>192.168.200.1</t>
         </is>
       </c>
-      <c r="H29" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I29" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J29" s="24" t="inlineStr">
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J29" s="17" t="inlineStr">
         <is>
           <t>Support host — BCM, K8s, Slurm, monitoring on the support VLAN</t>
         </is>
@@ -3063,7 +3083,7 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>bcm-02</t>
+          <t>support-02</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -3095,7 +3115,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J30" s="25" t="n"/>
+      <c r="J30" s="18" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -3105,7 +3125,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>k8s-01</t>
+          <t>support-03</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -3127,17 +3147,17 @@
           <t>192.168.200.1</t>
         </is>
       </c>
-      <c r="H31" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I31" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J31" s="24" t="n"/>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J31" s="17" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -3147,7 +3167,7 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>k8s-02</t>
+          <t>support-04</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -3179,7 +3199,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J32" s="25" t="n"/>
+      <c r="J32" s="18" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -3189,7 +3209,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>k8s-03</t>
+          <t>support-05</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -3211,17 +3231,17 @@
           <t>192.168.200.1</t>
         </is>
       </c>
-      <c r="H33" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I33" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J33" s="24" t="n"/>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J33" s="17" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -3231,7 +3251,7 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>slurm-01</t>
+          <t>support-06</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -3263,7 +3283,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="J34" s="25" t="n"/>
+      <c r="J34" s="18" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
@@ -3273,7 +3293,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>slurm-02</t>
+          <t>support-07</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -3295,17 +3315,17 @@
           <t>192.168.200.1</t>
         </is>
       </c>
-      <c r="H35" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I35" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="J35" s="24" t="n"/>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J35" s="17" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n"/>
@@ -3317,7 +3337,7 @@
       <c r="G36" s="1" t="n"/>
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
-      <c r="J36" s="25" t="n"/>
+      <c r="J36" s="18" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="n"/>
@@ -3327,9 +3347,9 @@
       <c r="E37" s="8" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
-      <c r="H37" s="18" t="n"/>
-      <c r="I37" s="18" t="n"/>
-      <c r="J37" s="24" t="n"/>
+      <c r="H37" s="11" t="n"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="17" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n"/>
@@ -3341,7 +3361,7 @@
       <c r="G38" s="1" t="n"/>
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="n"/>
-      <c r="J38" s="25" t="n"/>
+      <c r="J38" s="18" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="n"/>
@@ -3351,9 +3371,9 @@
       <c r="E39" s="8" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
-      <c r="H39" s="18" t="n"/>
-      <c r="I39" s="18" t="n"/>
-      <c r="J39" s="24" t="n"/>
+      <c r="H39" s="11" t="n"/>
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="17" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n"/>
@@ -3365,7 +3385,7 @@
       <c r="G40" s="1" t="n"/>
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
-      <c r="J40" s="25" t="n"/>
+      <c r="J40" s="18" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="n"/>
@@ -3375,9 +3395,9 @@
       <c r="E41" s="8" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
-      <c r="H41" s="18" t="n"/>
-      <c r="I41" s="18" t="n"/>
-      <c r="J41" s="24" t="n"/>
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="17" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n"/>
@@ -3389,7 +3409,7 @@
       <c r="G42" s="1" t="n"/>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
-      <c r="J42" s="25" t="n"/>
+      <c r="J42" s="18" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="n"/>
@@ -3399,9 +3419,9 @@
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
-      <c r="H43" s="18" t="n"/>
-      <c r="I43" s="18" t="n"/>
-      <c r="J43" s="24" t="n"/>
+      <c r="H43" s="11" t="n"/>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="17" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n"/>
@@ -3413,7 +3433,7 @@
       <c r="G44" s="1" t="n"/>
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
-      <c r="J44" s="25" t="n"/>
+      <c r="J44" s="18" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="n"/>
@@ -3423,9 +3443,9 @@
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
-      <c r="H45" s="18" t="n"/>
-      <c r="I45" s="18" t="n"/>
-      <c r="J45" s="24" t="n"/>
+      <c r="H45" s="11" t="n"/>
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="17" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n"/>
@@ -3437,7 +3457,7 @@
       <c r="G46" s="1" t="n"/>
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="n"/>
-      <c r="J46" s="25" t="n"/>
+      <c r="J46" s="18" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="n"/>
@@ -3447,9 +3467,9 @@
       <c r="E47" s="8" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
-      <c r="H47" s="18" t="n"/>
-      <c r="I47" s="18" t="n"/>
-      <c r="J47" s="24" t="n"/>
+      <c r="H47" s="11" t="n"/>
+      <c r="I47" s="11" t="n"/>
+      <c r="J47" s="17" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n"/>
@@ -3461,7 +3481,7 @@
       <c r="G48" s="1" t="n"/>
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="n"/>
-      <c r="J48" s="25" t="n"/>
+      <c r="J48" s="18" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="n"/>
@@ -3471,9 +3491,9 @@
       <c r="E49" s="8" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
-      <c r="H49" s="18" t="n"/>
-      <c r="I49" s="18" t="n"/>
-      <c r="J49" s="24" t="n"/>
+      <c r="H49" s="11" t="n"/>
+      <c r="I49" s="11" t="n"/>
+      <c r="J49" s="17" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n"/>
@@ -3485,7 +3505,7 @@
       <c r="G50" s="1" t="n"/>
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="n"/>
-      <c r="J50" s="25" t="n"/>
+      <c r="J50" s="18" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="n"/>
@@ -3495,9 +3515,9 @@
       <c r="E51" s="8" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
-      <c r="H51" s="18" t="n"/>
-      <c r="I51" s="18" t="n"/>
-      <c r="J51" s="24" t="n"/>
+      <c r="H51" s="11" t="n"/>
+      <c r="I51" s="11" t="n"/>
+      <c r="J51" s="17" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n"/>
@@ -3509,7 +3529,7 @@
       <c r="G52" s="1" t="n"/>
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="n"/>
-      <c r="J52" s="25" t="n"/>
+      <c r="J52" s="18" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="n"/>
@@ -3519,9 +3539,9 @@
       <c r="E53" s="8" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
-      <c r="H53" s="18" t="n"/>
-      <c r="I53" s="18" t="n"/>
-      <c r="J53" s="24" t="n"/>
+      <c r="H53" s="11" t="n"/>
+      <c r="I53" s="11" t="n"/>
+      <c r="J53" s="17" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n"/>
@@ -3533,7 +3553,7 @@
       <c r="G54" s="1" t="n"/>
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n"/>
-      <c r="J54" s="25" t="n"/>
+      <c r="J54" s="18" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="n"/>
@@ -3543,69 +3563,69 @@
       <c r="E55" s="8" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
-      <c r="H55" s="18" t="n"/>
-      <c r="I55" s="18" t="n"/>
-      <c r="J55" s="24" t="n"/>
+      <c r="H55" s="11" t="n"/>
+      <c r="I55" s="11" t="n"/>
+      <c r="J55" s="17" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="n"/>
-      <c r="B56" s="17" t="n"/>
-      <c r="C56" s="17" t="n"/>
-      <c r="D56" s="17" t="n"/>
-      <c r="E56" s="17" t="n"/>
-      <c r="F56" s="17" t="n"/>
-      <c r="G56" s="17" t="n"/>
+      <c r="A56" s="10" t="n"/>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
       <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="n"/>
-      <c r="J56" s="26" t="n"/>
+      <c r="J56" s="19" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="n"/>
-      <c r="B57" s="17" t="n"/>
-      <c r="C57" s="17" t="n"/>
-      <c r="D57" s="17" t="n"/>
-      <c r="E57" s="17" t="n"/>
-      <c r="F57" s="17" t="n"/>
-      <c r="G57" s="17" t="n"/>
+      <c r="A57" s="10" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
       <c r="H57" s="3" t="n"/>
       <c r="I57" s="3" t="n"/>
-      <c r="J57" s="26" t="n"/>
+      <c r="J57" s="19" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="17" t="n"/>
-      <c r="B58" s="17" t="n"/>
-      <c r="C58" s="17" t="n"/>
-      <c r="D58" s="17" t="n"/>
-      <c r="E58" s="17" t="n"/>
-      <c r="F58" s="17" t="n"/>
-      <c r="G58" s="17" t="n"/>
+      <c r="A58" s="10" t="n"/>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
       <c r="H58" s="3" t="n"/>
       <c r="I58" s="3" t="n"/>
-      <c r="J58" s="26" t="n"/>
+      <c r="J58" s="19" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="n"/>
-      <c r="B59" s="17" t="n"/>
-      <c r="C59" s="17" t="n"/>
-      <c r="D59" s="17" t="n"/>
-      <c r="E59" s="17" t="n"/>
-      <c r="F59" s="17" t="n"/>
-      <c r="G59" s="17" t="n"/>
+      <c r="A59" s="10" t="n"/>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
       <c r="H59" s="3" t="n"/>
       <c r="I59" s="3" t="n"/>
-      <c r="J59" s="26" t="n"/>
+      <c r="J59" s="19" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="17" t="n"/>
-      <c r="B60" s="17" t="n"/>
-      <c r="C60" s="17" t="n"/>
-      <c r="D60" s="17" t="n"/>
-      <c r="E60" s="17" t="n"/>
-      <c r="F60" s="17" t="n"/>
-      <c r="G60" s="17" t="n"/>
+      <c r="A60" s="10" t="n"/>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
       <c r="H60" s="3" t="n"/>
       <c r="I60" s="3" t="n"/>
-      <c r="J60" s="26" t="n"/>
+      <c r="J60" s="19" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -3629,48 +3649,48 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" style="64" min="1" max="7"/>
+    <col width="18" customWidth="1" style="59" min="1" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.1" customHeight="1" s="64">
-      <c r="A1" s="63" t="inlineStr">
+    <row r="1" ht="32.1" customHeight="1" s="59">
+      <c r="A1" s="58" t="inlineStr">
         <is>
           <t>Per-switch / per-VRF loopback overrides. Blank cells fall back to Settings.loopback_base. See docs/LOOPBACKS.md.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Switch</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>OOB</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>INBAND</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>GPU</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>STORAGE</t>
         </is>
@@ -3885,14 +3905,14 @@
   <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" style="64" min="1" max="1"/>
-    <col width="30" customWidth="1" style="64" min="2" max="2"/>
-    <col width="26.42578125" customWidth="1" style="64" min="3" max="3"/>
-    <col width="16" customWidth="1" style="64" min="4" max="4"/>
-    <col width="16.140625" customWidth="1" style="64" min="5" max="5"/>
-    <col width="13.42578125" customWidth="1" style="64" min="6" max="6"/>
-    <col width="12" customWidth="1" style="64" min="7" max="7"/>
-    <col width="23.42578125" customWidth="1" style="64" min="8" max="8"/>
+    <col width="25" customWidth="1" style="59" min="1" max="1"/>
+    <col width="30" customWidth="1" style="59" min="2" max="2"/>
+    <col width="26.42578125" customWidth="1" style="59" min="3" max="3"/>
+    <col width="16" customWidth="1" style="59" min="4" max="4"/>
+    <col width="16.140625" customWidth="1" style="59" min="5" max="5"/>
+    <col width="13.42578125" customWidth="1" style="59" min="6" max="6"/>
+    <col width="12" customWidth="1" style="59" min="7" max="7"/>
+    <col width="23.42578125" customWidth="1" style="59" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3909,7 +3929,7 @@
       <c r="G1" s="6" t="n"/>
       <c r="H1" s="6" t="n"/>
     </row>
-    <row r="2" ht="45" customHeight="1" s="64">
+    <row r="2" ht="45" customHeight="1" s="59">
       <c r="A2" s="7" t="inlineStr">
         <is>
           <t>VLAN ID</t>
@@ -3945,7 +3965,7 @@
           <t>VNI</t>
         </is>
       </c>
-      <c r="H2" s="21" t="inlineStr">
+      <c r="H2" s="14" t="inlineStr">
         <is>
           <t>DHCP Relay Client
 (No or comma separated VRF list of upstream)</t>
@@ -3984,7 +4004,7 @@
       <c r="G3" s="8" t="n">
         <v>4200</v>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="11" t="inlineStr">
         <is>
           <t>OOB</t>
         </is>
@@ -4060,7 +4080,7 @@
       <c r="G5" s="8" t="n">
         <v>4400</v>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
@@ -4136,7 +4156,7 @@
       <c r="G7" s="8" t="n">
         <v>4900</v>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4180,7 +4200,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
@@ -4303,7 +4322,6 @@
         <v>3005</v>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
@@ -4383,22 +4401,22 @@
           <t>Trunk</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="56" t="n">
         <v>300</v>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>200,400</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="n"/>
+      <c r="D20" s="56" t="inlineStr">
+        <is>
+          <t>300,400</t>
+        </is>
+      </c>
+      <c r="E20" s="56" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" s="18" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>100G</t>
         </is>
@@ -4421,11 +4439,11 @@
           <t>Access</t>
         </is>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="57" t="n">
         <v>900</v>
       </c>
-      <c r="D21" s="1" t="n"/>
-      <c r="E21" s="1" t="n"/>
+      <c r="D21" s="57" t="n"/>
+      <c r="E21" s="57" t="n"/>
       <c r="F21" s="1" t="n"/>
       <c r="G21" s="1" t="inlineStr">
         <is>
@@ -4455,18 +4473,18 @@
           <t>Access</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="56" t="n">
         <v>200</v>
       </c>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
+      <c r="D22" s="56" t="n"/>
+      <c r="E22" s="56" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H22" s="18" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>1G</t>
         </is>
@@ -4485,15 +4503,15 @@
           <t>Trunk</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="57" t="n">
         <v>500</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D23" s="57" t="inlineStr">
         <is>
           <t>400,500</t>
         </is>
       </c>
-      <c r="E23" s="1" t="inlineStr">
+      <c r="E23" s="57" t="inlineStr">
         <is>
           <t>300</t>
         </is>
@@ -4527,15 +4545,15 @@
           <t>Trunk</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="56" t="n">
         <v>400</v>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="56" t="inlineStr">
         <is>
           <t>200,300,400</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="56" t="inlineStr">
         <is>
           <t>300</t>
         </is>
@@ -4546,7 +4564,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>100G</t>
         </is>
@@ -4569,9 +4587,9 @@
           <t>L3</t>
         </is>
       </c>
-      <c r="C25" s="1" t="n"/>
-      <c r="D25" s="1" t="n"/>
-      <c r="E25" s="1" t="n"/>
+      <c r="C25" s="57" t="n"/>
+      <c r="D25" s="57" t="n"/>
+      <c r="E25" s="57" t="n"/>
       <c r="F25" s="1" t="inlineStr">
         <is>
           <t>default</t>
@@ -4605,9 +4623,9 @@
           <t>L3</t>
         </is>
       </c>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
+      <c r="C26" s="56" t="n"/>
+      <c r="D26" s="56" t="n"/>
+      <c r="E26" s="56" t="n"/>
       <c r="F26" s="8" t="inlineStr">
         <is>
           <t>EXIT</t>
@@ -4618,7 +4636,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H26" s="18" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>100G</t>
         </is>
@@ -4641,9 +4659,9 @@
           <t>L2</t>
         </is>
       </c>
-      <c r="C27" s="1" t="n"/>
-      <c r="D27" s="1" t="n"/>
-      <c r="E27" s="1" t="n"/>
+      <c r="C27" s="57" t="n"/>
+      <c r="D27" s="57" t="n"/>
+      <c r="E27" s="57" t="n"/>
       <c r="F27" s="1" t="n"/>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -4673,9 +4691,9 @@
           <t>L3</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
+      <c r="C28" s="56" t="n"/>
+      <c r="D28" s="56" t="n"/>
+      <c r="E28" s="56" t="n"/>
       <c r="F28" s="8" t="inlineStr">
         <is>
           <t>STORAGE</t>
@@ -4686,7 +4704,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H28" s="18" t="inlineStr">
+      <c r="H28" s="11" t="inlineStr">
         <is>
           <t>100G</t>
         </is>
@@ -4701,9 +4719,9 @@
     <row r="29">
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="1" t="n"/>
-      <c r="C29" s="1" t="n"/>
-      <c r="D29" s="1" t="n"/>
-      <c r="E29" s="1" t="n"/>
+      <c r="C29" s="57" t="n"/>
+      <c r="D29" s="57" t="n"/>
+      <c r="E29" s="57" t="n"/>
       <c r="F29" s="1" t="n"/>
       <c r="G29" s="1" t="n"/>
       <c r="H29" s="2" t="n"/>
@@ -4711,17 +4729,17 @@
       <c r="J29" s="1" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="20" t="n"/>
-      <c r="G30" s="20" t="n"/>
-      <c r="H30" s="20" t="n"/>
-      <c r="I30" s="20" t="n"/>
-      <c r="J30" s="20" t="n"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" s="64">
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="13" t="n"/>
+      <c r="G30" s="13" t="n"/>
+      <c r="H30" s="13" t="n"/>
+      <c r="I30" s="13" t="n"/>
+      <c r="J30" s="13" t="n"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" s="59">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>DHCP Relay</t>
@@ -4730,20 +4748,20 @@
       <c r="B31" s="4" t="n"/>
       <c r="C31" s="4" t="n"/>
     </row>
-    <row r="32" ht="45" customHeight="1" s="64">
-      <c r="A32" s="22" t="inlineStr">
+    <row r="32" ht="45" customHeight="1" s="59">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>Server IP
 (IP or comma separated list)</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>VRF
 (VRF reachable)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>Upstream Interface
 (Interface where reachable)</t>
@@ -4813,20 +4831,20 @@
   <dimension ref="A1:J434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14.140625" customWidth="1" style="64" min="1" max="1"/>
-    <col width="20.140625" customWidth="1" style="64" min="2" max="2"/>
-    <col width="24" customWidth="1" style="64" min="3" max="3"/>
-    <col width="18.42578125" customWidth="1" style="64" min="4" max="5"/>
-    <col width="17.140625" customWidth="1" style="64" min="6" max="6"/>
-    <col width="26.140625" customWidth="1" style="64" min="7" max="7"/>
-    <col width="12" customWidth="1" style="64" min="8" max="8"/>
-    <col width="13.5703125" customWidth="1" style="64" min="9" max="9"/>
-    <col width="25.5703125" customWidth="1" style="64" min="10" max="10"/>
-    <col width="16" customWidth="1" style="64" min="11" max="11"/>
-    <col width="22" customWidth="1" style="64" min="12" max="12"/>
-    <col width="12" customWidth="1" style="64" min="13" max="13"/>
-    <col width="16" customWidth="1" style="64" min="14" max="14"/>
-    <col width="14" customWidth="1" style="64" min="15" max="15"/>
+    <col width="14.140625" customWidth="1" style="59" min="1" max="1"/>
+    <col width="20.140625" customWidth="1" style="59" min="2" max="2"/>
+    <col width="24" customWidth="1" style="59" min="3" max="3"/>
+    <col width="18.42578125" customWidth="1" style="59" min="4" max="5"/>
+    <col width="17.140625" customWidth="1" style="59" min="6" max="6"/>
+    <col width="26.140625" customWidth="1" style="59" min="7" max="7"/>
+    <col width="12" customWidth="1" style="59" min="8" max="8"/>
+    <col width="13.5703125" customWidth="1" style="59" min="9" max="9"/>
+    <col width="25.5703125" customWidth="1" style="59" min="10" max="10"/>
+    <col width="16" customWidth="1" style="59" min="11" max="11"/>
+    <col width="22" customWidth="1" style="59" min="12" max="12"/>
+    <col width="12" customWidth="1" style="59" min="13" max="13"/>
+    <col width="16" customWidth="1" style="59" min="14" max="14"/>
+    <col width="14" customWidth="1" style="59" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4889,7 +4907,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -4937,7 +4955,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -4985,7 +5003,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -5033,7 +5051,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -5081,7 +5099,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
@@ -5129,7 +5147,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -5177,7 +5195,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -5225,7 +5243,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
@@ -5273,7 +5291,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -5321,7 +5339,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
@@ -5369,7 +5387,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -5417,7 +5435,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -5465,7 +5483,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -5513,7 +5531,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -5561,7 +5579,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -5609,7 +5627,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -5657,7 +5675,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -5705,7 +5723,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -5753,7 +5771,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -5801,7 +5819,7 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -5849,7 +5867,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -5897,7 +5915,7 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -5945,7 +5963,7 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -5993,7 +6011,7 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -6041,7 +6059,7 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -6089,7 +6107,7 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -6137,7 +6155,7 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -6185,7 +6203,7 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -6233,7 +6251,7 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -6281,7 +6299,7 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -6329,7 +6347,7 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -6377,7 +6395,7 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -6425,7 +6443,7 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -6473,7 +6491,7 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -6521,7 +6539,7 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -6569,7 +6587,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -6617,7 +6635,7 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -6665,7 +6683,7 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -6713,7 +6731,7 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -6761,7 +6779,7 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -6809,7 +6827,7 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -6857,7 +6875,7 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -6905,7 +6923,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -6953,7 +6971,7 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -7001,7 +7019,7 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -7049,7 +7067,7 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -7097,7 +7115,7 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -7145,7 +7163,7 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -7193,7 +7211,7 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -7241,7 +7259,7 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -7289,7 +7307,7 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -7337,7 +7355,7 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -7385,7 +7403,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -7433,7 +7451,7 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -7481,7 +7499,7 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -7529,7 +7547,7 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -7577,7 +7595,7 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -7625,7 +7643,7 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -7673,7 +7691,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -7721,7 +7739,7 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -7769,7 +7787,7 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -7817,7 +7835,7 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -7865,7 +7883,7 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -7913,7 +7931,7 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -7961,7 +7979,7 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -8009,7 +8027,7 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -8057,7 +8075,7 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -8105,7 +8123,7 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -8153,7 +8171,7 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -8201,7 +8219,7 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -8249,7 +8267,7 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -8297,7 +8315,7 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -8345,7 +8363,7 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -8393,7 +8411,7 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -8441,7 +8459,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -8489,7 +8507,7 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -8537,7 +8555,7 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -8585,7 +8603,7 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -8633,7 +8651,7 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -8681,7 +8699,7 @@
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -8729,7 +8747,7 @@
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -8777,7 +8795,7 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -8825,7 +8843,7 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -8873,7 +8891,7 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -8921,7 +8939,7 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
@@ -8969,7 +8987,7 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -9017,7 +9035,7 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -9065,7 +9083,7 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -9113,7 +9131,7 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -9161,7 +9179,7 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -9209,7 +9227,7 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -9257,7 +9275,7 @@
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
@@ -9305,7 +9323,7 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -9353,7 +9371,7 @@
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -9401,7 +9419,7 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -9449,7 +9467,7 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -9497,7 +9515,7 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -9545,7 +9563,7 @@
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -9593,7 +9611,7 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -9641,7 +9659,7 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -9689,7 +9707,7 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -9737,7 +9755,7 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -9785,7 +9803,7 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -9833,7 +9851,7 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -9881,7 +9899,7 @@
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -9929,7 +9947,7 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -9977,7 +9995,7 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -10025,7 +10043,7 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -10073,7 +10091,7 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -10121,7 +10139,7 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -10169,7 +10187,7 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
@@ -10217,7 +10235,7 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -10265,7 +10283,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -10313,7 +10331,7 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -10361,7 +10379,7 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -10409,7 +10427,7 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -10457,7 +10475,7 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -10505,7 +10523,7 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -10553,7 +10571,7 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
@@ -10601,7 +10619,7 @@
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
@@ -10649,7 +10667,7 @@
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
@@ -10697,7 +10715,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -10745,7 +10763,7 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -10793,7 +10811,7 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
@@ -10841,7 +10859,7 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
@@ -10889,7 +10907,7 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
@@ -10937,7 +10955,7 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
@@ -10985,7 +11003,7 @@
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
@@ -11033,7 +11051,7 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
@@ -11081,7 +11099,7 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
@@ -11129,7 +11147,7 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -11177,7 +11195,7 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
@@ -11225,7 +11243,7 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
@@ -11273,7 +11291,7 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -11321,7 +11339,7 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -11369,7 +11387,7 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
@@ -11417,7 +11435,7 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -11465,7 +11483,7 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -11513,7 +11531,7 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
@@ -11561,7 +11579,7 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -11609,7 +11627,7 @@
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
@@ -11657,7 +11675,7 @@
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
@@ -11705,7 +11723,7 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -11753,7 +11771,7 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -11801,7 +11819,7 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
@@ -11849,7 +11867,7 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
@@ -11897,7 +11915,7 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
@@ -11945,7 +11963,7 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -11993,7 +12011,7 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -12041,7 +12059,7 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
@@ -12089,7 +12107,7 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -12137,7 +12155,7 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
@@ -12185,7 +12203,7 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
@@ -12233,7 +12251,7 @@
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
@@ -12281,7 +12299,7 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -12329,7 +12347,7 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -12377,7 +12395,7 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -12425,7 +12443,7 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -12473,7 +12491,7 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -12521,7 +12539,7 @@
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -12569,7 +12587,7 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -12617,7 +12635,7 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -12665,7 +12683,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -12713,7 +12731,7 @@
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -12761,7 +12779,7 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -12809,7 +12827,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -12857,7 +12875,7 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -12905,7 +12923,7 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -12953,7 +12971,7 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -13001,7 +13019,7 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -13049,7 +13067,7 @@
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -13097,7 +13115,7 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -13145,7 +13163,7 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -13193,7 +13211,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -13241,7 +13259,7 @@
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -13289,7 +13307,7 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -13337,7 +13355,7 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>bcm-01</t>
+          <t>support-01</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -13383,7 +13401,7 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>bcm-01</t>
+          <t>support-01</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -13429,7 +13447,7 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>bcm-01</t>
+          <t>support-01</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -13477,7 +13495,7 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>bcm-01</t>
+          <t>support-01</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -13525,7 +13543,7 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>bcm-01</t>
+          <t>support-01</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -13573,7 +13591,7 @@
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>bcm-01</t>
+          <t>support-01</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -13621,7 +13639,7 @@
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>bcm-02</t>
+          <t>support-02</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -13667,7 +13685,7 @@
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>bcm-02</t>
+          <t>support-02</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -13713,7 +13731,7 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>bcm-02</t>
+          <t>support-02</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -13761,7 +13779,7 @@
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>bcm-02</t>
+          <t>support-02</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -13809,7 +13827,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>bcm-02</t>
+          <t>support-02</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -13857,7 +13875,7 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>bcm-02</t>
+          <t>support-02</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -13905,7 +13923,7 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>k8s-01</t>
+          <t>support-03</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -13951,7 +13969,7 @@
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>k8s-01</t>
+          <t>support-03</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -13997,7 +14015,7 @@
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>k8s-01</t>
+          <t>support-03</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
@@ -14045,7 +14063,7 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>k8s-01</t>
+          <t>support-03</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
@@ -14093,7 +14111,7 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>k8s-01</t>
+          <t>support-03</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -14141,7 +14159,7 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>k8s-01</t>
+          <t>support-03</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
@@ -14189,7 +14207,7 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>k8s-02</t>
+          <t>support-04</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
@@ -14235,7 +14253,7 @@
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>k8s-02</t>
+          <t>support-04</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
@@ -14281,7 +14299,7 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>k8s-02</t>
+          <t>support-04</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
@@ -14329,7 +14347,7 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>k8s-02</t>
+          <t>support-04</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
@@ -14377,7 +14395,7 @@
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>k8s-02</t>
+          <t>support-04</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
@@ -14425,7 +14443,7 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>k8s-02</t>
+          <t>support-04</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
@@ -14473,7 +14491,7 @@
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>k8s-03</t>
+          <t>support-05</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
@@ -14519,7 +14537,7 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>k8s-03</t>
+          <t>support-05</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
@@ -14565,7 +14583,7 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>k8s-03</t>
+          <t>support-05</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
@@ -14613,7 +14631,7 @@
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>k8s-03</t>
+          <t>support-05</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
@@ -14661,7 +14679,7 @@
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>k8s-03</t>
+          <t>support-05</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
@@ -14709,7 +14727,7 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>k8s-03</t>
+          <t>support-05</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
@@ -14757,7 +14775,7 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>slurm-01</t>
+          <t>support-06</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -14803,7 +14821,7 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>slurm-01</t>
+          <t>support-06</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
@@ -14849,7 +14867,7 @@
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t>slurm-01</t>
+          <t>support-06</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
@@ -14897,7 +14915,7 @@
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>slurm-01</t>
+          <t>support-06</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
@@ -14945,7 +14963,7 @@
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t>slurm-01</t>
+          <t>support-06</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
@@ -14993,7 +15011,7 @@
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>slurm-01</t>
+          <t>support-06</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
@@ -15041,7 +15059,7 @@
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>slurm-02</t>
+          <t>support-07</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
@@ -15087,7 +15105,7 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>slurm-02</t>
+          <t>support-07</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
@@ -15133,7 +15151,7 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>slurm-02</t>
+          <t>support-07</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
@@ -15181,7 +15199,7 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>slurm-02</t>
+          <t>support-07</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
@@ -15229,7 +15247,7 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>slurm-02</t>
+          <t>support-07</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
@@ -15277,7 +15295,7 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>slurm-02</t>
+          <t>support-07</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
@@ -19737,7 +19755,7 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>gpu-01</t>
+          <t>su-01-node-01</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
@@ -19773,7 +19791,7 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>gpu-02</t>
+          <t>su-01-node-02</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
@@ -19809,7 +19827,7 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>gpu-03</t>
+          <t>su-01-node-03</t>
         </is>
       </c>
       <c r="C317" s="1" t="inlineStr">
@@ -19845,7 +19863,7 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>gpu-04</t>
+          <t>su-01-node-04</t>
         </is>
       </c>
       <c r="C318" s="1" t="inlineStr">
@@ -19881,7 +19899,7 @@
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t>bcm-01</t>
+          <t>support-01</t>
         </is>
       </c>
       <c r="C319" s="1" t="inlineStr">
@@ -19917,7 +19935,7 @@
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t>k8s-01</t>
+          <t>support-03</t>
         </is>
       </c>
       <c r="C320" s="1" t="inlineStr">
@@ -19953,7 +19971,7 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t>k8s-02</t>
+          <t>support-04</t>
         </is>
       </c>
       <c r="C321" s="1" t="inlineStr">
@@ -19989,7 +20007,7 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t>slurm-01</t>
+          <t>support-06</t>
         </is>
       </c>
       <c r="C322" s="1" t="inlineStr">
@@ -20025,7 +20043,7 @@
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t>gpu-05</t>
+          <t>su-02-node-01</t>
         </is>
       </c>
       <c r="C323" s="1" t="inlineStr">
@@ -20061,7 +20079,7 @@
       </c>
       <c r="B324" s="1" t="inlineStr">
         <is>
-          <t>gpu-06</t>
+          <t>su-02-node-02</t>
         </is>
       </c>
       <c r="C324" s="1" t="inlineStr">
@@ -20097,7 +20115,7 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t>gpu-07</t>
+          <t>su-02-node-03</t>
         </is>
       </c>
       <c r="C325" s="1" t="inlineStr">
@@ -20133,7 +20151,7 @@
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t>gpu-08</t>
+          <t>su-02-node-04</t>
         </is>
       </c>
       <c r="C326" s="1" t="inlineStr">
@@ -20169,7 +20187,7 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t>bcm-02</t>
+          <t>support-02</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
@@ -20205,7 +20223,7 @@
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t>k8s-03</t>
+          <t>support-05</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
@@ -20241,7 +20259,7 @@
       </c>
       <c r="B329" s="1" t="inlineStr">
         <is>
-          <t>slurm-02</t>
+          <t>support-07</t>
         </is>
       </c>
       <c r="C329" s="1" t="inlineStr">
@@ -21546,8 +21564,8 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="64" min="1" max="1"/>
-    <col width="22" customWidth="1" style="64" min="2" max="2"/>
+    <col width="24" customWidth="1" style="59" min="1" max="1"/>
+    <col width="22" customWidth="1" style="59" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21586,7 +21604,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -21610,1155 +21627,172 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" style="64" min="1" max="1"/>
-    <col width="40" customWidth="1" style="64" min="2" max="2"/>
-    <col width="44" customWidth="1" style="64" min="3" max="3"/>
-    <col width="9.140625" customWidth="1" style="64" min="4" max="4"/>
+    <col width="41.85546875" customWidth="1" style="59" min="1" max="1"/>
+    <col width="63" customWidth="1" style="59" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>Reference — 2-8-9-400</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" s="64">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Read-only reference. Do not modify this sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>1. How This Excel Works</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Workflow</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" s="64">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>0. One-time: make air-setup</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Picks Air instance + stores credentials in a vault</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Required if deploying in Air</t>
+    <row r="1" ht="21" customHeight="1" s="59">
+      <c r="A1" s="60" t="inlineStr">
+        <is>
+          <t>ERA Switch Automation — Documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fill out this template, then run make import, make generate, and deploy. Start with README.md and the Excel Configuration Guide. Paths are relative to the project root.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20.25" customFormat="1" customHeight="1" s="61" thickBot="1">
+      <c r="A4" s="61" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="B4" s="61" t="inlineStr">
+        <is>
+          <t>What it covers</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" s="59" thickTop="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Start here — overview, prerequisites, and the end-to-end quick start</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>docs/EXCEL_CONFIGURATION_GUIDE.md</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>How to fill out every tab and field of this template</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>1. You fill out this Excel</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Settings, Nodes, and (if needed) Wire Map</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Describes your deployment</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" s="64">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>2. Run: make validate-excel EXCEL=&lt;this-file&gt;.xlsx</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Checks for errors before generating</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Catches mismatches early</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" s="64">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>3. Run: make deploy EXCEL=&lt;this-file&gt;.xlsx</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Generates inventory, configs, and Air topology</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>One command does everything</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" s="64">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>4. Test in NVIDIA Air (optional)</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Virtual simulation boots real Cumulus Linux</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Same configs as production</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" s="64">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>5. Deploy to physical hardware</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>ZTP provisions real switches with same configs</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>What you tested = what you deploy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>docs/ARCH_SUPPORT_MATRIX.md</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>What each architecture supports (topology, SU scaling, features)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>docs/AIR_DEPLOYMENT_GUIDE.md</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Deploy the generated configs in NVIDIA Air</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>docs/MANUAL_FALLBACK_GUIDE.md</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Deploy without the Air API (run from a management node)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>docs/ZTP_MODES.md</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Zero-Touch Provisioning: DHCP vs static-IP modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>docs/SECRETS_AND_VAULT.md</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Passwords and Ansible Vault</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>docs/LDAP_CONFIGURATION.md</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Optional LDAP authentication</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>What Each Sheet Does</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Sheet</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>Do I Edit It?</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" s="64">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Site name, architecture, subnets, LDAP, Air options</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>YES — customize for your deployment</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" s="64">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Nodes</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Every device: switches, servers, compute nodes with IPs and MACs</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>YES — set your management IPs and MACs</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" s="64">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>VLANs &amp; Profiles</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>VLAN definitions, VRF mappings, port profile configs</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Usually no — pre-configured for this architecture</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" s="64">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Wire Map</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Physical cabling: every cable from device A port X to switch B port Y</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>Usually no — unless your cabling differs from reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="64">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>Air_Only</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>Virtual infrastructure for NVIDIA Air simulation (see below)</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Usually no — pre-configured</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Reference (this sheet)</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>Architecture constants and guidance</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>NO — read-only</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>What is NVIDIA Air?</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1" s="64">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>NVIDIA Air is a cloud simulation platform.</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>It creates a virtual copy of your network so you can test configs before touching real hardware.</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="n"/>
-    </row>
-    <row r="24" ht="30" customHeight="1" s="64">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>The same Excel that generates your physical switch configs</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>also generates an Air topology JSON that builds the virtual environment.</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>What you test in Air = what gets deployed to production.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26" ht="30" customHeight="1" s="64">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>How Air Simulation Maps to This Excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>Concept</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>What It Means</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>Where in Excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1" s="64">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>Wire Map rows</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>Each row = one cable. Rows marked 'Display in Air = Yes' become virtual links.</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Wire Map sheet, column A</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1" s="64">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>Display in Air</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>Controls whether a physical cable also exists in the simulation. Set 'No' for things Air can't simulate (e.g. serial, BMC).</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>Wire Map column A, Air_Only column A</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1" s="64">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>Air_Only sheet</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>Virtual-only connections that don't exist on physical hardware. These create the simulation infrastructure (DHCP, management, internet).</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>Air_Only sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="45" customHeight="1" s="64">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>'Air - ' network profiles</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>Network profiles prefixed with 'Air - ' are simulation-only. They define how virtual infrastructure ports behave.</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>Air_Only 'Network Profile' column</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1" s="64">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>'outbound' switch role</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>Gives a virtual node internet access in Air. Not a real device — just tells Air to route traffic out.</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>Air_Only 'Switch Role' column</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="75" customHeight="1" s="64">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>Virtual nodes (auto-created)</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>dhcp-oob (DHCP server), oob-server-01 (ZTP/management gateway), air-oob-switch (virtual OOB switch). These are injected automatically — you don't add them.</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>Generated automatically from your settings</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1" s="64">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>Version mapping</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>Maps Cumulus version numbers (e.g. '5.16.1') to Air image file name. Pre-configured in Air_Only sheet.</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>Air_Only sheet, bottom section</t>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Common Mistakes to Avoid</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Mistake</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>What Goes Wrong</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>Do This Instead</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1" s="64">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>Putting /24 in the Mgmt IP column</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>Parser reads it as a string, not an IP</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>Put the IP in Mgmt IP, the prefix in the Prefix column</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1" s="64">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>Node Function doesn't match Wire Map System Role</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>Inventory and cabling disagree — configs will be wrong</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="inlineStr">
-        <is>
-          <t>Names must match exactly (case-sensitive)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1" s="64">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>management_switches count doesn't match mgmt_subnets</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>ZTP interfaces won't line up with OOB switches</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>If 3 subnets, set management_switches = 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1" s="64">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>Leaving MAC blank for physical (non-Air) deployments</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>ZTP can't identify switches without MACs</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="inlineStr">
-        <is>
-          <t>Enter real MACs for physical ZTP. Blank is OK for Air only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1" s="64">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Setting air_url / air_username / air_org in the Settings tab</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>Those fields moved out of the Excel — they're ignored now</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>Run make air-setup once per checkout</t>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>2. Architecture Overview</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="13" t="inlineStr">
-        <is>
-          <t>Architecture</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>2-8-9-400</t>
-        </is>
-      </c>
-      <c r="C46" s="13" t="inlineStr">
-        <is>
-          <t>ERA-00010 — 2 CPU, 8 GPU, 9 NIC, 400G</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>Nodes per SU</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="C47" s="13" t="inlineStr">
-        <is>
-          <t>All architectures use 4-node Scalable Units</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>Core Switches</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C48" s="13" t="inlineStr">
-        <is>
-          <t>core-01, core-02 (SN5610)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>OOB Switches</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="C49" s="13" t="inlineStr">
-        <is>
-          <t>oob-switch-01, -02, -03 (SN2201)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>Disabled Ports</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>54,56,58,60,62,64</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="inlineStr">
-        <is>
-          <t>Core switch ports disabled by default</t>
-        </is>
-      </c>
-    </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>Scaling</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="n"/>
-      <c r="B53" s="14" t="inlineStr">
-        <is>
-          <t>Architecture Max</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>SUs</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>Compute Nodes</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>Total GPUs</t>
-        </is>
-      </c>
-      <c r="B56" s="13" t="n">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>3. Network Defaults</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="13" t="inlineStr">
-        <is>
-          <t>BGP ASN</t>
-        </is>
-      </c>
-      <c r="B60" s="13" t="n">
-        <v>4260394788</v>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>Default; override in Settings tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="30" customHeight="1" s="64">
-      <c r="A61" s="13" t="inlineStr">
-        <is>
-          <t>Loopback Base</t>
-        </is>
-      </c>
-      <c r="B61" s="13" t="inlineStr">
-        <is>
-          <t>172.16.176</t>
-        </is>
-      </c>
-      <c r="C61" s="15" t="inlineStr">
-        <is>
-          <t>Default; override in Settings tab (4th octet auto-assigned per switch)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="30" customHeight="1" s="64">
-      <c r="A62" s="13" t="inlineStr">
-        <is>
-          <t>MH MAC</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="inlineStr">
-        <is>
-          <t>44:38:39:FF:00:AA</t>
-        </is>
-      </c>
-      <c r="C62" s="15" t="inlineStr">
-        <is>
-          <t>Default; EVPN Multihoming. Override in Settings if needed</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="30" customHeight="1" s="64">
-      <c r="A63" s="13" t="inlineStr">
-        <is>
-          <t>Anycast MAC</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="inlineStr">
-        <is>
-          <t>44:38:39:FF:00:FF</t>
-        </is>
-      </c>
-      <c r="C63" s="15" t="inlineStr">
-        <is>
-          <t>Default; VXLAN SVI gateway. Override in Settings if needed</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>Timezone</t>
-        </is>
-      </c>
-      <c r="B64" s="13" t="inlineStr">
-        <is>
-          <t>Etc/Zulu</t>
-        </is>
-      </c>
-      <c r="C64" s="15" t="inlineStr">
-        <is>
-          <t>Default; override in Settings tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>VNI Formula</t>
-        </is>
-      </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>VLAN ID + 4000</t>
-        </is>
-      </c>
-      <c r="C65" s="13" t="inlineStr">
-        <is>
-          <t>e.g. VLAN 300 = VNI 4300</t>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>Standard VLANs &amp; VRFs</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>VLAN</t>
-        </is>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>Name / VRF</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="inlineStr">
-        <is>
-          <t>L3 VNI</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="13" t="n">
-        <v>200</v>
-      </c>
-      <c r="B69" s="13" t="inlineStr">
-        <is>
-          <t>OOB  /  OOB VRF</t>
-        </is>
-      </c>
-      <c r="C69" s="13" t="inlineStr">
-        <is>
-          <t>5001</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="B70" s="13" t="inlineStr">
-        <is>
-          <t>CPU/In-Band  /  INBAND VRF</t>
-        </is>
-      </c>
-      <c r="C70" s="13" t="inlineStr">
-        <is>
-          <t>5002</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="13" t="n">
-        <v>400</v>
-      </c>
-      <c r="B71" s="13" t="inlineStr">
-        <is>
-          <t>Support  /  INBAND VRF</t>
-        </is>
-      </c>
-      <c r="C71" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="B72" s="13" t="inlineStr">
-        <is>
-          <t>Storage  /  INBAND VRF</t>
-        </is>
-      </c>
-      <c r="C72" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="13" t="n">
-        <v>900</v>
-      </c>
-      <c r="B73" s="13" t="inlineStr">
-        <is>
-          <t>GPU  /  GPU VRF</t>
-        </is>
-      </c>
-      <c r="C73" s="13" t="inlineStr">
-        <is>
-          <t>5003</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="inlineStr">
-        <is>
-          <t>EXIT VRF (no VLAN)</t>
-        </is>
-      </c>
-      <c r="C74" s="13" t="inlineStr">
-        <is>
-          <t>5004</t>
-        </is>
-      </c>
-    </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="12" t="inlineStr">
-        <is>
-          <t>Target Cumulus Versions</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="13" t="inlineStr">
-        <is>
-          <t>Core: 5.16.1</t>
-        </is>
-      </c>
-      <c r="B77" s="13" t="inlineStr">
-        <is>
-          <t>OOB: 5.15.0</t>
-        </is>
-      </c>
-      <c r="C77" s="13" t="inlineStr">
-        <is>
-          <t>See docs/NVUE_VERSION_COMPAT.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79">
-      <c r="A79" s="11" t="inlineStr">
-        <is>
-          <t>4. OOB Network — Choose One Option</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="12" t="inlineStr">
-        <is>
-          <t>Common IPs (both options)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="13" t="inlineStr">
-        <is>
-          <t>OOB VLAN: 200</t>
-        </is>
-      </c>
-      <c r="B81" s="13" t="inlineStr">
-        <is>
-          <t>Gateway: 192.168.200.1</t>
-        </is>
-      </c>
-      <c r="C81" s="13" t="inlineStr">
-        <is>
-          <t>ZTP Server: 192.168.200.100</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="13" t="inlineStr">
-        <is>
-          <t>OOB Switch IPs</t>
-        </is>
-      </c>
-      <c r="B82" s="13" t="inlineStr">
-        <is>
-          <t>oob-switch-01: .2,  -02: .3,  -03: .4</t>
-        </is>
-      </c>
-      <c r="C82" s="13" t="inlineStr">
-        <is>
-          <t>On 192.168.200.0/24</t>
-        </is>
-      </c>
-    </row>
-    <row r="83"/>
-    <row r="84">
-      <c r="A84" s="12" t="inlineStr">
-        <is>
-          <t>Option A — Flat OOB (single subnet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="14" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C85" s="14" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="13" t="inlineStr">
-        <is>
-          <t>mgmt_subnets</t>
-        </is>
-      </c>
-      <c r="B86" s="13" t="inlineStr">
-        <is>
-          <t>192.168.200.0/24</t>
-        </is>
-      </c>
-      <c r="C86" s="13" t="inlineStr">
-        <is>
-          <t>All OOB switches share one subnet</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="13" t="inlineStr">
-        <is>
-          <t>management_switches</t>
-        </is>
-      </c>
-      <c r="B87" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="C87" s="13" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="13" t="inlineStr">
-        <is>
-          <t>Best for</t>
-        </is>
-      </c>
-      <c r="B88" s="13" t="inlineStr">
-        <is>
-          <t>Simpler setups, Air simulations</t>
-        </is>
-      </c>
-      <c r="C88" s="13" t="n"/>
-    </row>
-    <row r="89"/>
-    <row r="90" ht="30" customHeight="1" s="64">
-      <c r="A90" s="12" t="inlineStr">
-        <is>
-          <t>Option B — Per-Switch OOB (one subnet per switch)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="14" t="inlineStr">
-        <is>
-          <t>Setting</t>
-        </is>
-      </c>
-      <c r="B91" s="14" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="n"/>
-    </row>
-    <row r="92" ht="30" customHeight="1" s="64">
-      <c r="A92" s="13" t="inlineStr">
-        <is>
-          <t>mgmt_subnets</t>
-        </is>
-      </c>
-      <c r="B92" s="13" t="inlineStr">
-        <is>
-          <t>192.168.200.0/24, 192.168.210.0/24, 192.168.220.0/24</t>
-        </is>
-      </c>
-      <c r="C92" s="13" t="inlineStr">
-        <is>
-          <t>Comma-separated, one CIDR per OOB switch</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="13" t="inlineStr">
-        <is>
-          <t>management_switches</t>
-        </is>
-      </c>
-      <c r="B93" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="C93" s="13" t="inlineStr">
-        <is>
-          <t>Must match number of subnets</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="13" t="inlineStr">
-        <is>
-          <t>Best for</t>
-        </is>
-      </c>
-      <c r="B94" s="13" t="inlineStr">
-        <is>
-          <t>Larger deployments, physical hardware</t>
-        </is>
-      </c>
-      <c r="C94" s="13" t="inlineStr">
-        <is>
-          <t>Separate broadcast domain per rack/pod</t>
-        </is>
-      </c>
-    </row>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>docs/README.md</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Full documentation index</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="59"/>
+    <row r="16" ht="30" customHeight="1" s="59"/>
+    <row r="17" ht="30" customHeight="1" s="59"/>
+    <row r="18" ht="30" customHeight="1" s="59"/>
+    <row r="19" ht="30" customHeight="1" s="59"/>
+    <row r="23" ht="45" customHeight="1" s="59"/>
+    <row r="24" ht="30" customHeight="1" s="59"/>
+    <row r="26" ht="30" customHeight="1" s="59"/>
+    <row r="28" ht="30" customHeight="1" s="59"/>
+    <row r="29" ht="45" customHeight="1" s="59"/>
+    <row r="30" ht="60" customHeight="1" s="59"/>
+    <row r="31" ht="45" customHeight="1" s="59"/>
+    <row r="32" ht="45" customHeight="1" s="59"/>
+    <row r="33" ht="75" customHeight="1" s="59"/>
+    <row r="34" ht="45" customHeight="1" s="59"/>
+    <row r="38" ht="30" customHeight="1" s="59"/>
+    <row r="39" ht="30" customHeight="1" s="59"/>
+    <row r="40" ht="30" customHeight="1" s="59"/>
+    <row r="41" ht="30" customHeight="1" s="59"/>
+    <row r="42" ht="30" customHeight="1" s="59"/>
+    <row r="61" ht="30" customHeight="1" s="59"/>
+    <row r="62" ht="30" customHeight="1" s="59"/>
+    <row r="63" ht="30" customHeight="1" s="59"/>
+    <row r="90" ht="30" customHeight="1" s="59"/>
+    <row r="92" ht="30" customHeight="1" s="59"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
